--- a/output/starter_budget_tracker/starter_budget_tracker.xlsx
+++ b/output/starter_budget_tracker/starter_budget_tracker.xlsx
@@ -7,9 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="My Budget" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Income" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Spending" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="START HERE" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Expenses" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Budget" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Savings Goals" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,8 +21,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="&quot;€&quot;#,##0.00"/>
+  </numFmts>
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,36 +34,70 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00DDDDDD"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00F97316"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00333333"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00777777"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00222222"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="18"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00888888"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="000D1B2A"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <color rgb="001A1A2E"/>
+      <sz val="12"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -66,17 +106,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000D1B2A"/>
+        <fgColor rgb="001A1A2E"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004361EE"/>
+        <fgColor rgb="00FFF7F0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFD166"/>
+        <fgColor rgb="0022C55E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EF4444"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F97316"/>
       </patternFill>
     </fill>
   </fills>
@@ -106,27 +156,78 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00EF4444"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FEE2E2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -197,6 +298,139 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Income vs Expenses</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Dashboard'!C9</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Dashboard'!$B$10:$B$21</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Dashboard'!$C$10:$C$21</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Dashboard'!D9</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Dashboard'!$B$10:$B$21</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Dashboard'!$D$10:$D$21</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -485,69 +719,119 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FF1A1A2E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="B2:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Starter Budget Tracker</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Income</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Spent</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Left</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="3">
-        <f>SUM(Income!B:B)</f>
-        <v/>
-      </c>
-      <c r="B4" s="3">
-        <f>SUM(Spending!C:C)</f>
-        <v/>
-      </c>
-      <c r="C4" s="3">
-        <f>B4-C4</f>
-        <v/>
-      </c>
-      <c r="D4" s="3">
-        <f>TEXT(D4/B4,"0%")</f>
-        <v/>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>💰  STARTER BUDGET TRACKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Welcome! You're 3 steps away from knowing exactly where your money goes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>STEP 1 — Add your income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Open the "Income" tab and log everything you earn: salary, freelance, side money. Just type the date, amount and pick a source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>STEP 2 — Log your expenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Open the "Expenses" tab every time you spend. Pick a category from the dropdown — this powers all the charts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>STEP 3 — Watch the Dashboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>The "Dashboard" tab updates itself: this month's income, spending, what's left, and your savings rate. Set limits in "Budget" and goals in "Savings Goals".</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>TIP: Delete the sample rows once you've seen how it works — select them and press Delete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>TIP: On Google Sheets? File → Make a copy first, then edit your own copy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>TIP: Everything recalculates automatically. You never need to touch a formula.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Need help? Message NasriTools on Etsy — I reply fast. Enjoy! 🧡</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+  <mergeCells count="12">
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B2:F3"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="B13:F13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -556,7 +840,503 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FF22C55E"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:G33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="30" customHeight="1">
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>📊  MY BUDGET DASHBOARD</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>THIS MONTH IN</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>THIS MONTH OUT</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>LEFT TO SPEND</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="B5" s="10">
+        <f>SUMPRODUCT((TEXT(Income!$A$2:$A$500,"yyyy-mm")=TEXT(TODAY(),"yyyy-mm"))*Income!$B$2:$B$500)</f>
+        <v/>
+      </c>
+      <c r="D5" s="11">
+        <f>SUMPRODUCT((TEXT(Expenses!$A$2:$A$500,"yyyy-mm")=TEXT(TODAY(),"yyyy-mm"))*Expenses!$D$2:$D$500)</f>
+        <v/>
+      </c>
+      <c r="F5" s="12">
+        <f>B5-D5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>MONTH-BY-MONTH (2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>Saved</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="C10" s="16">
+        <f>SUMPRODUCT((TEXT(Income!$A$2:$A$500,"yyyy-mm")="2026-01")*Income!$B$2:$B$500)</f>
+        <v/>
+      </c>
+      <c r="D10" s="16">
+        <f>SUMPRODUCT((TEXT(Expenses!$A$2:$A$500,"yyyy-mm")="2026-01")*Expenses!$D$2:$D$500)</f>
+        <v/>
+      </c>
+      <c r="E10" s="16">
+        <f>C10-D10</f>
+        <v/>
+      </c>
+      <c r="F10" s="17">
+        <f>IFERROR(TEXT(E10/C10,"0%"),"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="C11" s="19">
+        <f>SUMPRODUCT((TEXT(Income!$A$2:$A$500,"yyyy-mm")="2026-02")*Income!$B$2:$B$500)</f>
+        <v/>
+      </c>
+      <c r="D11" s="19">
+        <f>SUMPRODUCT((TEXT(Expenses!$A$2:$A$500,"yyyy-mm")="2026-02")*Expenses!$D$2:$D$500)</f>
+        <v/>
+      </c>
+      <c r="E11" s="19">
+        <f>C11-D11</f>
+        <v/>
+      </c>
+      <c r="F11" s="20">
+        <f>IFERROR(TEXT(E11/C11,"0%"),"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="C12" s="16">
+        <f>SUMPRODUCT((TEXT(Income!$A$2:$A$500,"yyyy-mm")="2026-03")*Income!$B$2:$B$500)</f>
+        <v/>
+      </c>
+      <c r="D12" s="16">
+        <f>SUMPRODUCT((TEXT(Expenses!$A$2:$A$500,"yyyy-mm")="2026-03")*Expenses!$D$2:$D$500)</f>
+        <v/>
+      </c>
+      <c r="E12" s="16">
+        <f>C12-D12</f>
+        <v/>
+      </c>
+      <c r="F12" s="17">
+        <f>IFERROR(TEXT(E12/C12,"0%"),"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="C13" s="19">
+        <f>SUMPRODUCT((TEXT(Income!$A$2:$A$500,"yyyy-mm")="2026-04")*Income!$B$2:$B$500)</f>
+        <v/>
+      </c>
+      <c r="D13" s="19">
+        <f>SUMPRODUCT((TEXT(Expenses!$A$2:$A$500,"yyyy-mm")="2026-04")*Expenses!$D$2:$D$500)</f>
+        <v/>
+      </c>
+      <c r="E13" s="19">
+        <f>C13-D13</f>
+        <v/>
+      </c>
+      <c r="F13" s="20">
+        <f>IFERROR(TEXT(E13/C13,"0%"),"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="C14" s="16">
+        <f>SUMPRODUCT((TEXT(Income!$A$2:$A$500,"yyyy-mm")="2026-05")*Income!$B$2:$B$500)</f>
+        <v/>
+      </c>
+      <c r="D14" s="16">
+        <f>SUMPRODUCT((TEXT(Expenses!$A$2:$A$500,"yyyy-mm")="2026-05")*Expenses!$D$2:$D$500)</f>
+        <v/>
+      </c>
+      <c r="E14" s="16">
+        <f>C14-D14</f>
+        <v/>
+      </c>
+      <c r="F14" s="17">
+        <f>IFERROR(TEXT(E14/C14,"0%"),"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="C15" s="19">
+        <f>SUMPRODUCT((TEXT(Income!$A$2:$A$500,"yyyy-mm")="2026-06")*Income!$B$2:$B$500)</f>
+        <v/>
+      </c>
+      <c r="D15" s="19">
+        <f>SUMPRODUCT((TEXT(Expenses!$A$2:$A$500,"yyyy-mm")="2026-06")*Expenses!$D$2:$D$500)</f>
+        <v/>
+      </c>
+      <c r="E15" s="19">
+        <f>C15-D15</f>
+        <v/>
+      </c>
+      <c r="F15" s="20">
+        <f>IFERROR(TEXT(E15/C15,"0%"),"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="C16" s="16">
+        <f>SUMPRODUCT((TEXT(Income!$A$2:$A$500,"yyyy-mm")="2026-07")*Income!$B$2:$B$500)</f>
+        <v/>
+      </c>
+      <c r="D16" s="16">
+        <f>SUMPRODUCT((TEXT(Expenses!$A$2:$A$500,"yyyy-mm")="2026-07")*Expenses!$D$2:$D$500)</f>
+        <v/>
+      </c>
+      <c r="E16" s="16">
+        <f>C16-D16</f>
+        <v/>
+      </c>
+      <c r="F16" s="17">
+        <f>IFERROR(TEXT(E16/C16,"0%"),"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="C17" s="19">
+        <f>SUMPRODUCT((TEXT(Income!$A$2:$A$500,"yyyy-mm")="2026-08")*Income!$B$2:$B$500)</f>
+        <v/>
+      </c>
+      <c r="D17" s="19">
+        <f>SUMPRODUCT((TEXT(Expenses!$A$2:$A$500,"yyyy-mm")="2026-08")*Expenses!$D$2:$D$500)</f>
+        <v/>
+      </c>
+      <c r="E17" s="19">
+        <f>C17-D17</f>
+        <v/>
+      </c>
+      <c r="F17" s="20">
+        <f>IFERROR(TEXT(E17/C17,"0%"),"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="C18" s="16">
+        <f>SUMPRODUCT((TEXT(Income!$A$2:$A$500,"yyyy-mm")="2026-09")*Income!$B$2:$B$500)</f>
+        <v/>
+      </c>
+      <c r="D18" s="16">
+        <f>SUMPRODUCT((TEXT(Expenses!$A$2:$A$500,"yyyy-mm")="2026-09")*Expenses!$D$2:$D$500)</f>
+        <v/>
+      </c>
+      <c r="E18" s="16">
+        <f>C18-D18</f>
+        <v/>
+      </c>
+      <c r="F18" s="17">
+        <f>IFERROR(TEXT(E18/C18,"0%"),"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="C19" s="19">
+        <f>SUMPRODUCT((TEXT(Income!$A$2:$A$500,"yyyy-mm")="2026-10")*Income!$B$2:$B$500)</f>
+        <v/>
+      </c>
+      <c r="D19" s="19">
+        <f>SUMPRODUCT((TEXT(Expenses!$A$2:$A$500,"yyyy-mm")="2026-10")*Expenses!$D$2:$D$500)</f>
+        <v/>
+      </c>
+      <c r="E19" s="19">
+        <f>C19-D19</f>
+        <v/>
+      </c>
+      <c r="F19" s="20">
+        <f>IFERROR(TEXT(E19/C19,"0%"),"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="C20" s="16">
+        <f>SUMPRODUCT((TEXT(Income!$A$2:$A$500,"yyyy-mm")="2026-11")*Income!$B$2:$B$500)</f>
+        <v/>
+      </c>
+      <c r="D20" s="16">
+        <f>SUMPRODUCT((TEXT(Expenses!$A$2:$A$500,"yyyy-mm")="2026-11")*Expenses!$D$2:$D$500)</f>
+        <v/>
+      </c>
+      <c r="E20" s="16">
+        <f>C20-D20</f>
+        <v/>
+      </c>
+      <c r="F20" s="17">
+        <f>IFERROR(TEXT(E20/C20,"0%"),"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="C21" s="19">
+        <f>SUMPRODUCT((TEXT(Income!$A$2:$A$500,"yyyy-mm")="2026-12")*Income!$B$2:$B$500)</f>
+        <v/>
+      </c>
+      <c r="D21" s="19">
+        <f>SUMPRODUCT((TEXT(Expenses!$A$2:$A$500,"yyyy-mm")="2026-12")*Expenses!$D$2:$D$500)</f>
+        <v/>
+      </c>
+      <c r="E21" s="19">
+        <f>C21-D21</f>
+        <v/>
+      </c>
+      <c r="F21" s="20">
+        <f>IFERROR(TEXT(E21/C21,"0%"),"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>SPENDING BY CATEGORY (all time)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>Spent</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>Housing</t>
+        </is>
+      </c>
+      <c r="C26" s="21">
+        <f>SUMIFS(Expenses!$D$2:$D$500,Expenses!$C$2:$C$500,B26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="18" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="C27" s="21">
+        <f>SUMIFS(Expenses!$D$2:$D$500,Expenses!$C$2:$C$500,B27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="C28" s="21">
+        <f>SUMIFS(Expenses!$D$2:$D$500,Expenses!$C$2:$C$500,B28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="18" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="C29" s="21">
+        <f>SUMIFS(Expenses!$D$2:$D$500,Expenses!$C$2:$C$500,B29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="18" t="inlineStr">
+        <is>
+          <t>Fun</t>
+        </is>
+      </c>
+      <c r="C30" s="21">
+        <f>SUMIFS(Expenses!$D$2:$D$500,Expenses!$C$2:$C$500,B30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="18" t="inlineStr">
+        <is>
+          <t>Shopping</t>
+        </is>
+      </c>
+      <c r="C31" s="21">
+        <f>SUMIFS(Expenses!$D$2:$D$500,Expenses!$C$2:$C$500,B31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="18" t="inlineStr">
+        <is>
+          <t>Bills</t>
+        </is>
+      </c>
+      <c r="C32" s="21">
+        <f>SUMIFS(Expenses!$D$2:$D$500,Expenses!$C$2:$C$500,B32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="18" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C33" s="21">
+        <f>SUMIFS(Expenses!$D$2:$D$500,Expenses!$C$2:$C$500,B33)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="B4:C4"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C26:C33">
+    <cfRule type="dataBar" priority="1">
+      <dataBar showValue="1">
+        <cfvo type="num" val="0"/>
+        <cfvo type="max"/>
+        <color rgb="00F97316"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -565,366 +1345,863 @@
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="14" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="14" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="14" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>2200</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr"/>
-      <c r="D2" s="5" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="22" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B2" s="23" t="n">
+        <v>2200</v>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>Salary</t>
+        </is>
+      </c>
+      <c r="D2" s="15" t="inlineStr">
         <is>
           <t>Monthly salary</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>2200</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr"/>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Monthly salary</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>2200</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Monthly salary</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>2200</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Monthly salary</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>2200</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Monthly salary</t>
+    <row r="3">
+      <c r="A3" s="24" t="n">
+        <v>46208</v>
+      </c>
+      <c r="B3" s="21" t="n">
+        <v>350</v>
+      </c>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>Freelance</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="inlineStr">
+        <is>
+          <t>Logo project</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="22" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B4" s="23" t="n">
+        <v>120</v>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Side Hustle</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>Etsy shop sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="24" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B5" s="21" t="n">
+        <v>60</v>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>Sold old phone</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="22" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B6" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Freelance</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>Consulting call</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="C2 C3 C4 C5 C6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Salary","Freelance","Side Hustle","Gift","Other"</formula1>
+    <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Salary,Freelance,Side Hustle,Gift,Other"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FFEF4444"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="22" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>Housing</t>
+        </is>
+      </c>
+      <c r="D2" s="23" t="n">
+        <v>750</v>
+      </c>
+      <c r="E2" s="15" t="inlineStr">
+        <is>
+          <t>Monthly rent</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="24" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="D3" s="21" t="n">
+        <v>82</v>
+      </c>
+      <c r="E3" s="18" t="inlineStr">
+        <is>
+          <t>Weekly shop</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="22" t="n">
+        <v>46206</v>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Metro card</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="D4" s="23" t="n">
+        <v>40</v>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>Monthly pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="24" t="n">
+        <v>46208</v>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>Pharmacy</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="n">
+        <v>18</v>
+      </c>
+      <c r="E5" s="18" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="22" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>Cinema</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Fun</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="n">
+        <v>24</v>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>Weekend movie</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="24" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="n">
+        <v>76</v>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>Weekly shop</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="22" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Electricity bill</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Bills</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="n">
+        <v>65</v>
+      </c>
+      <c r="E8" s="15" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="24" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>New shoes</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>Shopping</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="n">
+        <v>59</v>
+      </c>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>Summer sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="n">
+        <v>45</v>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>Dinner out</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="24" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="n">
+        <v>80</v>
+      </c>
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t>Weekly shop</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="n">
+        <v>46221</v>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>Internet bill</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>Bills</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="n">
+        <v>35</v>
+      </c>
+      <c r="E12" s="15" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="24" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>Fuel</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="n">
+        <v>55</v>
+      </c>
+      <c r="E13" s="18" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="n">
+        <v>74</v>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>Weekly shop</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="24" t="n">
+        <v>46228</v>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="n">
+        <v>30</v>
+      </c>
+      <c r="E15" s="18" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="22" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>Gift</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="n">
+        <v>25</v>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>Friend's birthday</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Housing,Food,Transport,Health,Fun,Shopping,Bills,Other"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>Amount</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr"/>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>Weekly shop</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr"/>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>Weekly shop</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>Weekly shop</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>Weekly shop</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>Weekly shop</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Weekly shop</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>Weekly shop</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Weekly shop</t>
-        </is>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>Monthly Budget</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>Spent This Month</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>Housing</t>
+        </is>
+      </c>
+      <c r="B2" s="23" t="n">
+        <v>800</v>
+      </c>
+      <c r="C2" s="23">
+        <f>SUMPRODUCT((TEXT(Expenses!$A$2:$A$500,"yyyy-mm")=TEXT(TODAY(),"yyyy-mm"))*(Expenses!$C$2:$C$500=A2)*Expenses!$D$2:$D$500)</f>
+        <v/>
+      </c>
+      <c r="D2" s="23">
+        <f>B2-C2</f>
+        <v/>
+      </c>
+      <c r="E2" s="25">
+        <f>IF(C2&gt;B2,"⚠ OVER","✓ OK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="B3" s="21" t="n">
+        <v>400</v>
+      </c>
+      <c r="C3" s="21">
+        <f>SUMPRODUCT((TEXT(Expenses!$A$2:$A$500,"yyyy-mm")=TEXT(TODAY(),"yyyy-mm"))*(Expenses!$C$2:$C$500=A3)*Expenses!$D$2:$D$500)</f>
+        <v/>
+      </c>
+      <c r="D3" s="21">
+        <f>B3-C3</f>
+        <v/>
+      </c>
+      <c r="E3" s="26">
+        <f>IF(C3&gt;B3,"⚠ OVER","✓ OK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="B4" s="23" t="n">
+        <v>120</v>
+      </c>
+      <c r="C4" s="23">
+        <f>SUMPRODUCT((TEXT(Expenses!$A$2:$A$500,"yyyy-mm")=TEXT(TODAY(),"yyyy-mm"))*(Expenses!$C$2:$C$500=A4)*Expenses!$D$2:$D$500)</f>
+        <v/>
+      </c>
+      <c r="D4" s="23">
+        <f>B4-C4</f>
+        <v/>
+      </c>
+      <c r="E4" s="25">
+        <f>IF(C4&gt;B4,"⚠ OVER","✓ OK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="n">
+        <v>80</v>
+      </c>
+      <c r="C5" s="21">
+        <f>SUMPRODUCT((TEXT(Expenses!$A$2:$A$500,"yyyy-mm")=TEXT(TODAY(),"yyyy-mm"))*(Expenses!$C$2:$C$500=A5)*Expenses!$D$2:$D$500)</f>
+        <v/>
+      </c>
+      <c r="D5" s="21">
+        <f>B5-C5</f>
+        <v/>
+      </c>
+      <c r="E5" s="26">
+        <f>IF(C5&gt;B5,"⚠ OVER","✓ OK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>Fun</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" s="23">
+        <f>SUMPRODUCT((TEXT(Expenses!$A$2:$A$500,"yyyy-mm")=TEXT(TODAY(),"yyyy-mm"))*(Expenses!$C$2:$C$500=A6)*Expenses!$D$2:$D$500)</f>
+        <v/>
+      </c>
+      <c r="D6" s="23">
+        <f>B6-C6</f>
+        <v/>
+      </c>
+      <c r="E6" s="25">
+        <f>IF(C6&gt;B6,"⚠ OVER","✓ OK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>Shopping</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" s="21">
+        <f>SUMPRODUCT((TEXT(Expenses!$A$2:$A$500,"yyyy-mm")=TEXT(TODAY(),"yyyy-mm"))*(Expenses!$C$2:$C$500=A7)*Expenses!$D$2:$D$500)</f>
+        <v/>
+      </c>
+      <c r="D7" s="21">
+        <f>B7-C7</f>
+        <v/>
+      </c>
+      <c r="E7" s="26">
+        <f>IF(C7&gt;B7,"⚠ OVER","✓ OK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>Bills</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="n">
+        <v>150</v>
+      </c>
+      <c r="C8" s="23">
+        <f>SUMPRODUCT((TEXT(Expenses!$A$2:$A$500,"yyyy-mm")=TEXT(TODAY(),"yyyy-mm"))*(Expenses!$C$2:$C$500=A8)*Expenses!$D$2:$D$500)</f>
+        <v/>
+      </c>
+      <c r="D8" s="23">
+        <f>B8-C8</f>
+        <v/>
+      </c>
+      <c r="E8" s="25">
+        <f>IF(C8&gt;B8,"⚠ OVER","✓ OK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="n">
+        <v>60</v>
+      </c>
+      <c r="C9" s="21">
+        <f>SUMPRODUCT((TEXT(Expenses!$A$2:$A$500,"yyyy-mm")=TEXT(TODAY(),"yyyy-mm"))*(Expenses!$C$2:$C$500=A9)*Expenses!$D$2:$D$500)</f>
+        <v/>
+      </c>
+      <c r="D9" s="21">
+        <f>B9-C9</f>
+        <v/>
+      </c>
+      <c r="E9" s="26">
+        <f>IF(C9&gt;B9,"⚠ OVER","✓ OK")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="D2 D3 D4 D5 D6 D7 D8 D9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Housing","Food","Transport","Fun","Health","Other"</formula1>
-    </dataValidation>
-  </dataValidations>
+  <conditionalFormatting sqref="D2:D9">
+    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E9">
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="0">
+      <formula>"⚠ OVER"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>Goal</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>Saved So Far</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>Progress</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t>Emergency Fund</t>
+        </is>
+      </c>
+      <c r="B2" s="21" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C2" s="21" t="n">
+        <v>850</v>
+      </c>
+      <c r="D2" s="27">
+        <f>IFERROR(C2/B2,0)</f>
+        <v/>
+      </c>
+      <c r="E2" s="18" t="inlineStr">
+        <is>
+          <t>3 months of expenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>Summer Trip</t>
+        </is>
+      </c>
+      <c r="B3" s="21" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C3" s="21" t="n">
+        <v>400</v>
+      </c>
+      <c r="D3" s="27">
+        <f>IFERROR(C3/B3,0)</f>
+        <v/>
+      </c>
+      <c r="E3" s="18" t="inlineStr">
+        <is>
+          <t>July next year</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>New Laptop</t>
+        </is>
+      </c>
+      <c r="B4" s="21" t="n">
+        <v>900</v>
+      </c>
+      <c r="C4" s="21" t="n">
+        <v>620</v>
+      </c>
+      <c r="D4" s="27">
+        <f>IFERROR(C4/B4,0)</f>
+        <v/>
+      </c>
+      <c r="E4" s="18" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D2:D50">
+    <cfRule type="dataBar" priority="1">
+      <dataBar showValue="1">
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="0022C55E"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>